--- a/artfynd/A 1254-2025 artfynd.xlsx
+++ b/artfynd/A 1254-2025 artfynd.xlsx
@@ -7818,7 +7818,7 @@
         <v>118602466</v>
       </c>
       <c r="B72" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>119124880</v>
       </c>
       <c r="B100" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>119124881</v>
       </c>
       <c r="B114" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 1254-2025 artfynd.xlsx
+++ b/artfynd/A 1254-2025 artfynd.xlsx
@@ -7818,7 +7818,7 @@
         <v>118602466</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>119124880</v>
       </c>
       <c r="B100" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>119124881</v>
       </c>
       <c r="B114" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>

--- a/artfynd/A 1254-2025 artfynd.xlsx
+++ b/artfynd/A 1254-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY178"/>
+  <dimension ref="A1:AZ178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602845</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602877</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602513</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602515</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602517</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602518</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602862</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602864</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602445</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602446</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602447</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602449</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602450</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602835</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602849</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602484</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602486</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602857</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602858</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602457</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602840</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602424</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124771</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124772</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124773</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124774</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124775</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124776</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124777</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602552</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125066</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125067</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125068</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125069</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602554</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124831</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125064</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124941</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602524</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602525</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602526</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602527</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602528</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602529</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602530</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602531</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602532</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602533</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602534</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602535</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602536</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602537</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602538</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602539</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,6 +6690,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602542</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6492,6 +6792,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602543</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6589,6 +6894,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602544</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6686,6 +6996,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602546</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6783,6 +7098,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602547</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6880,6 +7200,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124964</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6977,6 +7302,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124965</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7074,6 +7404,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124966</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7171,6 +7506,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124967</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7268,6 +7608,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124968</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7365,6 +7710,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124969</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7462,6 +7812,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124970</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7559,6 +7914,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124971</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7656,6 +8016,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124973</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7753,6 +8118,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124974</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7850,6 +8220,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124975</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7947,6 +8322,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124976</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8044,6 +8424,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124978</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8141,6 +8526,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124979</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8238,6 +8628,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124980</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8335,6 +8730,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124981</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8432,6 +8832,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124982</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8529,6 +8934,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124984</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8626,6 +9036,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124985</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8723,6 +9138,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124986</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8820,6 +9240,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124987</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8917,6 +9342,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124988</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9014,6 +9444,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124989</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9111,6 +9546,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124990</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9208,6 +9648,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124991</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9305,6 +9750,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124992</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9402,6 +9852,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124993</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9499,6 +9954,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124994</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9596,6 +10056,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124995</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9693,6 +10158,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124996</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9790,6 +10260,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124997</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9887,6 +10362,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124998</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9984,6 +10464,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124999</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10081,6 +10566,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125000</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10178,6 +10668,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125001</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10275,6 +10770,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125002</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10372,6 +10872,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125003</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10469,6 +10974,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125004</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10566,6 +11076,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125005</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10663,6 +11178,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125006</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10760,6 +11280,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125007</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10857,6 +11382,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125008</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10954,6 +11484,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125009</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11051,6 +11586,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125010</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11148,6 +11688,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125011</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11245,6 +11790,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125012</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11342,6 +11892,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125013</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11439,6 +11994,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602422</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11536,6 +12096,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602423</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11633,6 +12198,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124762</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11730,6 +12300,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124763</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11827,6 +12402,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124764</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11924,6 +12504,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602500</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12021,6 +12606,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602501</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12118,6 +12708,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602502</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12215,6 +12810,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602503</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12312,6 +12912,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602504</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12409,6 +13014,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602505</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12506,6 +13116,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602506</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12603,6 +13218,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602507</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12700,6 +13320,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602508</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12797,6 +13422,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602510</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12894,6 +13524,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124950</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -12991,6 +13626,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124866</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13088,6 +13728,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124867</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13185,6 +13830,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124868</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13282,6 +13932,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602438</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13379,6 +14034,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602439</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13476,6 +14136,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602440</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13573,6 +14238,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602441</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13670,6 +14340,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602442</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13767,6 +14442,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602444</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13864,6 +14544,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124792</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -13961,6 +14646,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124793</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14058,6 +14748,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124794</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14155,6 +14850,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124796</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14252,6 +14952,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124797</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14349,6 +15054,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124799</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14446,6 +15156,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124800</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14543,6 +15258,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124801</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14640,6 +15360,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124802</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14737,6 +15462,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124803</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14834,6 +15564,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602555</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14944,6 +15679,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602466</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15054,6 +15794,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124880</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15164,6 +15909,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124881</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15269,6 +16019,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124836</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15378,6 +16133,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124940</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15475,6 +16235,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602548</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15572,6 +16337,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602549</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15669,6 +16439,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602550</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15766,6 +16541,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125062</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15863,6 +16643,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125063</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15961,6 +16746,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124937</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16059,6 +16849,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124938</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16156,6 +16951,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602479</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16253,6 +17053,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602480</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16350,6 +17155,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602481</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16447,6 +17257,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602482</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16544,6 +17359,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602483</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16641,6 +17461,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124904</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16738,6 +17563,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124905</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16835,6 +17665,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124906</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16932,6 +17767,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124910</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17029,6 +17869,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124911</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17126,6 +17971,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124912</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17223,6 +18073,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124913</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17320,6 +18175,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124915</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17417,6 +18277,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602454</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17514,6 +18379,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602455</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17611,6 +18481,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118602456</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17708,6 +18583,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124818</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17805,6 +18685,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124819</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17902,8 +18787,192 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119124820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>